--- a/Input_Data_Sheets/SOIL_parameters.xlsx
+++ b/Input_Data_Sheets/SOIL_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcu\Documents\GitHub\HydroPol2D\Input_Data_Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mngomes/Documents/GitHub/HydroPol2D/Input_Data_Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8725196-B0F8-436C-A0E0-812D391FB49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD6D3D9-5A2C-2D44-9695-A9648FBBFEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SOIL_parameters" sheetId="1" r:id="rId1"/>
@@ -35,96 +35,304 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={00540091-00D0-46A1-A217-00DE00800055}</author>
-    <author>tc={00FF00CD-00F8-46FF-8C00-002B00CF0026}</author>
-    <author>tc={006100CE-00A5-44D3-8950-0096001B0083}</author>
-    <author>tc={00E4009B-0000-458E-A9BB-0064002200AF}</author>
-    <author>tc={00C4009F-0065-4BE7-9884-0000009600ED}</author>
-    <author>tc={0094002A-00E3-4659-8CFF-0076009D0006}</author>
-    <author>tc={00B700F0-00BE-4DA2-8B1A-00F9005100C6}</author>
-    <author>tc={00E70088-00F0-4345-B3D2-005E0040007F}</author>
-    <author>tc={C3BAAA68-AA56-6911-7386-C2F7E29C1DD6}</author>
+    <author>Marcus Gomes</author>
   </authors>
   <commentList>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{00540091-00D0-46A1-A217-00DE00800055}">
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{3965E51E-7E4B-1A4B-88D1-9B071D907210}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Soil vertical saturated hydraulic conductivity
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Marcus Gomes:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Saturated Hydraulic Conductivity </t>
+        </r>
       </text>
     </comment>
-    <comment ref="D2" authorId="1" shapeId="0" xr:uid="{00FF00CD-00F8-46FF-8C00-002B00CF0026}">
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{CA933AAF-7841-6842-B5F1-D474807082CC}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Suction head
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Marcus Gomes:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>van-Genutchen n parameter</t>
+        </r>
       </text>
     </comment>
-    <comment ref="E2" authorId="2" shapeId="0" xr:uid="{006100CE-00A5-44D3-8950-0096001B0083}">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{36304D63-1DEC-B940-BE72-89B4750CF836}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Initial soil moisture when not using an initial soil moisture map
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Marcus Gomes:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>van-Genutchen alpha parameter</t>
+        </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="3" shapeId="0" xr:uid="{00E4009B-0000-458E-A9BB-0064002200AF}">
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{4A370307-914A-AA49-9D54-4671EAEC1906}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Porosity
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Marcus Gomes:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Saturated porosity</t>
+        </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="4" shapeId="0" xr:uid="{00C4009F-0065-4BE7-9884-0000009600ED}">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{C23017C0-AC39-DB49-840C-6B9B4A99E074}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Residual porosity
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Marcus Gomes:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Residual porosity</t>
+        </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="5" shapeId="0" xr:uid="{0094002A-00E3-4659-8CFF-0076009D0006}">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{B20558BE-79CA-5B46-A77B-74E1B4795A87}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Unstaturated zone reservoir coefficient (assuming a linear reservoir)
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Marcus Gomes:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Initial water content</t>
+        </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="6" shapeId="0" xr:uid="{00B700F0-00BE-4DA2-8B1A-00F9005100C6}">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{1CB820FA-F992-5D4A-88D4-D3FEC6578C11}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Drainable porosity for the perched aquifer
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Marcus Gomes:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Shallow aquifer drainable porosity</t>
+        </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="7" shapeId="0" xr:uid="{00E70088-00F0-4345-B3D2-005E0040007F}">
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{E9B669D3-BBBB-104D-B90C-5E77C0C7BF37}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Horizontal saturated hydraulic conductivity
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Marcus Gomes:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Lateral saturated hydraulic conductivity for shallow aquifer</t>
+        </r>
       </text>
     </comment>
-    <comment ref="K2" authorId="8" shapeId="0" xr:uid="{C3BAAA68-AA56-6911-7386-C2F7E29C1DD6}">
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{DEB7B12F-1D51-204C-947D-DB397CDE46CE}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Distance to bedrock [m] if not entered as a raster
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Marcus Gomes:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Distance to bedrock</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -132,7 +340,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>HydroPol2D - Soil Parameters</t>
   </si>
@@ -174,21 +382,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>ψ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Garamond"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (mm)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>I</t>
+      <t>θ</t>
     </r>
     <r>
       <rPr>
@@ -198,17 +392,137 @@
         <rFont val="Garamond"/>
         <family val="1"/>
       </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Garamond"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (mm)</t>
-    </r>
+      <t>sat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Garamond"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (cm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Garamond"/>
+        <family val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Garamond"/>
+        <family val="1"/>
+      </rPr>
+      <t>.cm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Garamond"/>
+        <family val="1"/>
+      </rPr>
+      <t>-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Garamond"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Sy [-]</t>
+  </si>
+  <si>
+    <r>
+      <t>k</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Garamond"/>
+        <family val="1"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Garamond"/>
+        <family val="1"/>
+      </rPr>
+      <t>sat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Garamond"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (mm/h)</t>
+    </r>
+  </si>
+  <si>
+    <t>DTB (m)</t>
+  </si>
+  <si>
+    <t>Clay</t>
+  </si>
+  <si>
+    <t>Silty Clay</t>
+  </si>
+  <si>
+    <t>Sandy Clay</t>
+  </si>
+  <si>
+    <t>Clay Loam</t>
+  </si>
+  <si>
+    <t>Silty Clay Loam</t>
+  </si>
+  <si>
+    <t>Sandy Clay Loam</t>
+  </si>
+  <si>
+    <t>Silty Loam</t>
+  </si>
+  <si>
+    <t>Loam</t>
+  </si>
+  <si>
+    <t>Sandy Loam</t>
+  </si>
+  <si>
+    <t>Silt</t>
+  </si>
+  <si>
+    <t>Loamy Sand</t>
+  </si>
+  <si>
+    <t>Sand</t>
+  </si>
+  <si>
+    <t>n [-]</t>
+  </si>
+  <si>
+    <t>alpha [1/m]</t>
   </si>
   <si>
     <r>
@@ -218,17 +532,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>θ</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Garamond"/>
-        <family val="1"/>
-      </rPr>
-      <t>sat</t>
+      <t>θr</t>
     </r>
     <r>
       <rPr>
@@ -286,17 +590,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>θ</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Garamond"/>
-        <family val="1"/>
-      </rPr>
-      <t>i</t>
+      <t>θi</t>
     </r>
     <r>
       <rPr>
@@ -347,90 +641,14 @@
     </r>
   </si>
   <si>
-    <t>k (1/h)</t>
-  </si>
-  <si>
-    <t>Sy [-]</t>
-  </si>
-  <si>
-    <r>
-      <t>k</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Garamond"/>
-        <family val="1"/>
-      </rPr>
-      <t>g</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Garamond"/>
-        <family val="1"/>
-      </rPr>
-      <t>sat</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Garamond"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (mm/h)</t>
-    </r>
-  </si>
-  <si>
-    <t>DTB (m)</t>
-  </si>
-  <si>
-    <t>Clay</t>
-  </si>
-  <si>
-    <t>Silty Clay</t>
-  </si>
-  <si>
-    <t>Sandy Clay</t>
-  </si>
-  <si>
-    <t>Clay Loam</t>
-  </si>
-  <si>
-    <t>Silty Clay Loam</t>
-  </si>
-  <si>
-    <t>Sandy Clay Loam</t>
-  </si>
-  <si>
-    <t>Silty Loam</t>
-  </si>
-  <si>
-    <t>Loam</t>
-  </si>
-  <si>
-    <t>Sandy Loam</t>
-  </si>
-  <si>
-    <t>Silt</t>
-  </si>
-  <si>
-    <t>Loamy Sand</t>
-  </si>
-  <si>
-    <t>Sand</t>
+    <t>Water</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -475,6 +693,25 @@
       <color theme="1"/>
       <name val="Garamond"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Garamond"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -549,7 +786,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -568,6 +805,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -595,16 +835,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>171449</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>257175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>392614</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>77062</xdr:rowOff>
+      <xdr:rowOff>45312</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -636,12 +876,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Marcus Nóbrega" id="{72918DFE-2EE6-5A5B-06BF-AE3622538093}" userId="" providerId=""/>
-</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -852,80 +1086,40 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C2" personId="{72918DFE-2EE6-5A5B-06BF-AE3622538093}" id="{00540091-00D0-46A1-A217-00DE00800055}">
-    <text xml:space="preserve">Soil vertical saturated hydraulic conductivity
-</text>
-  </threadedComment>
-  <threadedComment ref="D2" personId="{72918DFE-2EE6-5A5B-06BF-AE3622538093}" id="{00FF00CD-00F8-46FF-8C00-002B00CF0026}">
-    <text xml:space="preserve">Suction head
-</text>
-  </threadedComment>
-  <threadedComment ref="E2" personId="{72918DFE-2EE6-5A5B-06BF-AE3622538093}" id="{006100CE-00A5-44D3-8950-0096001B0083}">
-    <text xml:space="preserve">Initial soil moisture when not using an initial soil moisture map
-</text>
-  </threadedComment>
-  <threadedComment ref="F2" personId="{72918DFE-2EE6-5A5B-06BF-AE3622538093}" id="{00E4009B-0000-458E-A9BB-0064002200AF}">
-    <text xml:space="preserve">Porosity
-</text>
-  </threadedComment>
-  <threadedComment ref="G2" personId="{72918DFE-2EE6-5A5B-06BF-AE3622538093}" id="{00C4009F-0065-4BE7-9884-0000009600ED}">
-    <text xml:space="preserve">Residual porosity
-</text>
-  </threadedComment>
-  <threadedComment ref="H2" personId="{72918DFE-2EE6-5A5B-06BF-AE3622538093}" id="{0094002A-00E3-4659-8CFF-0076009D0006}">
-    <text xml:space="preserve">Unstaturated zone reservoir coefficient (assuming a linear reservoir)
-</text>
-  </threadedComment>
-  <threadedComment ref="I2" personId="{72918DFE-2EE6-5A5B-06BF-AE3622538093}" id="{00B700F0-00BE-4DA2-8B1A-00F9005100C6}">
-    <text xml:space="preserve">Drainable porosity for the perched aquifer
-</text>
-  </threadedComment>
-  <threadedComment ref="J2" personId="{72918DFE-2EE6-5A5B-06BF-AE3622538093}" id="{00E70088-00F0-4345-B3D2-005E0040007F}">
-    <text xml:space="preserve">Horizontal saturated hydraulic conductivity
-</text>
-  </threadedComment>
-  <threadedComment ref="K2" personId="{72918DFE-2EE6-5A5B-06BF-AE3622538093}" id="{C3BAAA68-AA56-6911-7386-C2F7E29C1DD6}">
-    <text xml:space="preserve">Distance to bedrock [m] if not entered as a raster
-</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M46"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.85546875" style="1"/>
-    <col min="6" max="6" width="16.28515625" style="1" customWidth="1"/>
-    <col min="7" max="11" width="19.140625" style="1" customWidth="1"/>
-    <col min="12" max="13" width="6.5703125" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="17.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.83203125" style="1"/>
+    <col min="6" max="6" width="16.33203125" style="1" customWidth="1"/>
+    <col min="7" max="12" width="19.1640625" style="1" customWidth="1"/>
+    <col min="13" max="14" width="6.5" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:14" ht="25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
       <c r="L1" s="11"/>
-      <c r="M1" s="2"/>
-    </row>
-    <row r="2" spans="1:13" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="M1" s="12"/>
+      <c r="N1" s="2"/>
+    </row>
+    <row r="2" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -936,35 +1130,35 @@
         <v>3</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="M2" s="4"/>
+      <c r="N2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="B3" s="7">
         <v>1</v>
@@ -973,36 +1167,35 @@
         <v>0.3</v>
       </c>
       <c r="D3" s="7">
-        <v>316.3</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="E3" s="7">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="F3" s="7">
         <v>0.38500000000000001</v>
       </c>
       <c r="G3" s="7">
-        <v>1.0000000000000001E-5</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="H3" s="7">
-        <v>5.0000000000000002E-5</v>
+        <v>0.2</v>
       </c>
       <c r="I3" s="7">
         <v>0.03</v>
       </c>
       <c r="J3" s="7">
-        <f t="shared" ref="J3:J14" si="0">20*C3</f>
         <v>6</v>
       </c>
       <c r="K3" s="6">
         <v>1</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="5"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M3" s="4"/>
+      <c r="N3" s="5"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B4" s="7">
         <v>2</v>
@@ -1011,36 +1204,35 @@
         <v>0.5</v>
       </c>
       <c r="D4" s="7">
-        <v>292.2</v>
+        <v>1.23</v>
       </c>
       <c r="E4" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F4" s="7">
         <v>0.42299999999999999</v>
       </c>
       <c r="G4" s="7">
-        <v>1E-4</v>
+        <v>8.8999999999999996E-2</v>
       </c>
       <c r="H4" s="7">
-        <v>5.0000000000000002E-5</v>
+        <v>0.22</v>
       </c>
       <c r="I4" s="7">
         <v>0.04</v>
       </c>
       <c r="J4" s="7">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="K4" s="6">
         <v>1</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="5"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M4" s="4"/>
+      <c r="N4" s="5"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B5" s="7">
         <v>3</v>
@@ -1049,36 +1241,35 @@
         <v>0.6</v>
       </c>
       <c r="D5" s="7">
-        <v>239</v>
+        <v>1.31</v>
       </c>
       <c r="E5" s="7">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="F5" s="7">
         <v>0.32100000000000001</v>
       </c>
       <c r="G5" s="7">
-        <v>1E-4</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="H5" s="7">
-        <v>5.0000000000000002E-5</v>
+        <v>0.17</v>
       </c>
       <c r="I5" s="7">
         <v>0.06</v>
       </c>
       <c r="J5" s="7">
-        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="K5" s="6">
         <v>1</v>
       </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="5"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M5" s="4"/>
+      <c r="N5" s="5"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B6" s="7">
         <v>4</v>
@@ -1087,36 +1278,35 @@
         <v>1</v>
       </c>
       <c r="D6" s="7">
-        <v>208.8</v>
+        <v>1.31</v>
       </c>
       <c r="E6" s="7">
-        <v>10</v>
+        <v>1.9</v>
       </c>
       <c r="F6" s="7">
         <v>0.309</v>
       </c>
       <c r="G6" s="7">
-        <v>1E-4</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="H6" s="7">
-        <v>5.0000000000000002E-5</v>
+        <v>0.16</v>
       </c>
       <c r="I6" s="7">
         <v>0.08</v>
       </c>
       <c r="J6" s="7">
-        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="K6" s="6">
         <v>1</v>
       </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M6" s="4"/>
+      <c r="N6" s="5"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B7" s="7">
         <v>5</v>
@@ -1125,36 +1315,35 @@
         <v>1</v>
       </c>
       <c r="D7" s="7">
-        <v>273</v>
+        <v>1.23</v>
       </c>
       <c r="E7" s="7">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="F7" s="7">
         <v>0.432</v>
       </c>
       <c r="G7" s="7">
-        <v>1E-4</v>
+        <v>8.8999999999999996E-2</v>
       </c>
       <c r="H7" s="7">
-        <v>5.0000000000000002E-5</v>
+        <v>0.22</v>
       </c>
       <c r="I7" s="7">
         <v>0.09</v>
       </c>
       <c r="J7" s="7">
-        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="K7" s="6">
         <v>1</v>
       </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="5"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M7" s="4"/>
+      <c r="N7" s="5"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B8" s="7">
         <v>6</v>
@@ -1163,36 +1352,35 @@
         <v>1.5</v>
       </c>
       <c r="D8" s="7">
-        <v>218.5</v>
+        <v>1.48</v>
       </c>
       <c r="E8" s="7">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F8" s="7">
         <v>0.33</v>
       </c>
       <c r="G8" s="7">
-        <v>1E-4</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="H8" s="7">
-        <v>5.0000000000000002E-5</v>
+        <v>0.17</v>
       </c>
       <c r="I8" s="7">
         <v>0.11</v>
       </c>
       <c r="J8" s="7">
-        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="K8" s="6">
         <v>1</v>
       </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="5"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M8" s="4"/>
+      <c r="N8" s="5"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B9" s="7">
         <v>7</v>
@@ -1201,36 +1389,35 @@
         <v>7.6</v>
       </c>
       <c r="D9" s="7">
-        <v>88.9</v>
+        <v>1.41</v>
       </c>
       <c r="E9" s="7">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="F9" s="7">
         <v>0.434</v>
       </c>
       <c r="G9" s="7">
-        <v>1E-4</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="H9" s="7">
-        <v>5.0000000000000002E-5</v>
+        <v>0.22</v>
       </c>
       <c r="I9" s="7">
         <v>0.14000000000000001</v>
       </c>
       <c r="J9" s="7">
-        <f t="shared" si="0"/>
         <v>152</v>
       </c>
       <c r="K9" s="6">
         <v>1</v>
       </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="5"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M9" s="4"/>
+      <c r="N9" s="5"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B10" s="7">
         <v>8</v>
@@ -1239,36 +1426,35 @@
         <v>3.4</v>
       </c>
       <c r="D10" s="7">
-        <v>166.8</v>
+        <v>1.56</v>
       </c>
       <c r="E10" s="7">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="F10" s="7">
         <v>0.48599999999999999</v>
       </c>
       <c r="G10" s="7">
-        <v>1E-4</v>
+        <v>7.8E-2</v>
       </c>
       <c r="H10" s="7">
-        <v>5.0000000000000002E-5</v>
+        <v>0.25</v>
       </c>
       <c r="I10" s="7">
         <v>0.18</v>
       </c>
       <c r="J10" s="7">
-        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="K10" s="6">
         <v>1</v>
       </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="5"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M10" s="4"/>
+      <c r="N10" s="5"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B11" s="7">
         <v>9</v>
@@ -1277,36 +1463,35 @@
         <v>10.9</v>
       </c>
       <c r="D11" s="7">
-        <v>110.1</v>
+        <v>1.89</v>
       </c>
       <c r="E11" s="7">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="F11" s="7">
         <v>0.41199999999999998</v>
       </c>
       <c r="G11" s="7">
-        <v>1E-4</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="H11" s="7">
-        <v>5.0000000000000002E-5</v>
+        <v>0.21</v>
       </c>
       <c r="I11" s="7">
         <v>0.22</v>
       </c>
       <c r="J11" s="7">
-        <f t="shared" si="0"/>
         <v>218</v>
       </c>
       <c r="K11" s="6">
         <v>1</v>
       </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="5"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M11" s="4"/>
+      <c r="N11" s="5"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B12" s="7">
         <v>10</v>
@@ -1315,36 +1500,35 @@
         <v>3.4</v>
       </c>
       <c r="D12" s="7">
-        <v>166.8</v>
+        <v>1.37</v>
       </c>
       <c r="E12" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F12" s="7">
         <v>0.48599999999999999</v>
       </c>
       <c r="G12" s="7">
-        <v>1E-4</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="H12" s="7">
-        <v>5.0000000000000002E-5</v>
+        <v>0.24</v>
       </c>
       <c r="I12" s="7">
         <v>0.12</v>
       </c>
       <c r="J12" s="7">
-        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="K12" s="6">
         <v>1</v>
       </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="5"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M12" s="4"/>
+      <c r="N12" s="5"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B13" s="7">
         <v>11</v>
@@ -1353,36 +1537,35 @@
         <v>29.9</v>
       </c>
       <c r="D13" s="7">
-        <v>61.3</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="E13" s="7">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="F13" s="7">
         <v>0.40100000000000002</v>
       </c>
       <c r="G13" s="7">
-        <v>1E-4</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="H13" s="7">
-        <v>5.0000000000000002E-5</v>
+        <v>0.2</v>
       </c>
       <c r="I13" s="7">
         <v>0.25</v>
       </c>
       <c r="J13" s="7">
-        <f t="shared" si="0"/>
         <v>598</v>
       </c>
       <c r="K13" s="6">
         <v>1</v>
       </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M13" s="4"/>
+      <c r="N13" s="5"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B14" s="7">
         <v>12</v>
@@ -1391,49 +1574,71 @@
         <v>117.8</v>
       </c>
       <c r="D14" s="7">
-        <v>49.5</v>
+        <v>2.68</v>
       </c>
       <c r="E14" s="7">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="F14" s="7">
         <v>0.41699999999999998</v>
       </c>
       <c r="G14" s="7">
-        <v>1E-4</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="H14" s="7">
-        <v>5.0000000000000002E-5</v>
+        <v>0.21</v>
       </c>
       <c r="I14" s="7">
         <v>0.3</v>
       </c>
       <c r="J14" s="7">
-        <f t="shared" si="0"/>
         <v>2356</v>
       </c>
       <c r="K14" s="6">
         <v>1</v>
       </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="5"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="5"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M14" s="4"/>
+      <c r="N14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="F15" s="7">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="G15" s="7">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="I15" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="J15" s="7">
+        <v>6</v>
+      </c>
+      <c r="K15" s="6">
+        <v>1</v>
+      </c>
+      <c r="L15" s="6"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="5"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
@@ -1444,11 +1649,12 @@
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="5"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K16" s="7"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="5"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
@@ -1459,11 +1665,12 @@
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="5"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K17" s="7"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="5"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
@@ -1474,11 +1681,12 @@
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="5"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K18" s="7"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="5"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
@@ -1489,11 +1697,12 @@
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="5"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K19" s="7"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="5"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
@@ -1504,11 +1713,12 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="5"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K20" s="7"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="5"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
@@ -1519,11 +1729,12 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="5"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K21" s="7"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="5"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
@@ -1534,11 +1745,12 @@
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="5"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K22" s="7"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="5"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
@@ -1549,99 +1761,100 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="5"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L25" s="4"/>
-      <c r="M25" s="5"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L26" s="4"/>
-      <c r="M26" s="5"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L27" s="4"/>
-      <c r="M27" s="5"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L28" s="4"/>
-      <c r="M28" s="5"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L29" s="4"/>
-      <c r="M29" s="5"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L30" s="4"/>
-      <c r="M30" s="5"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L31" s="4"/>
-      <c r="M31" s="5"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L32" s="4"/>
-      <c r="M32" s="5"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L33" s="4"/>
-      <c r="M33" s="5"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L34" s="4"/>
-      <c r="M34" s="5"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L35" s="4"/>
-      <c r="M35" s="5"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L37" s="4"/>
-      <c r="M37" s="5"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L38" s="4"/>
-      <c r="M38" s="5"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L40" s="4"/>
-      <c r="M40" s="5"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L41" s="4"/>
-      <c r="M41" s="5"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L43" s="4"/>
-      <c r="M43" s="5"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L44" s="4"/>
-      <c r="M44" s="5"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L45" s="4"/>
-      <c r="M45" s="5"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K23" s="7"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="5"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M24" s="4"/>
+      <c r="N24" s="5"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M25" s="4"/>
+      <c r="N25" s="5"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M26" s="4"/>
+      <c r="N26" s="5"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M27" s="4"/>
+      <c r="N27" s="5"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M28" s="4"/>
+      <c r="N28" s="5"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M29" s="4"/>
+      <c r="N29" s="5"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M30" s="4"/>
+      <c r="N30" s="5"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M31" s="4"/>
+      <c r="N31" s="5"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M32" s="4"/>
+      <c r="N32" s="5"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M33" s="4"/>
+      <c r="N33" s="5"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M34" s="4"/>
+      <c r="N34" s="5"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M35" s="4"/>
+      <c r="N35" s="5"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M36" s="4"/>
+      <c r="N36" s="5"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M37" s="4"/>
+      <c r="N37" s="5"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M38" s="4"/>
+      <c r="N38" s="5"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M39" s="4"/>
+      <c r="N39" s="5"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M40" s="4"/>
+      <c r="N40" s="5"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M41" s="4"/>
+      <c r="N41" s="5"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M42" s="4"/>
+      <c r="N42" s="5"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M43" s="4"/>
+      <c r="N43" s="5"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M44" s="4"/>
+      <c r="N44" s="5"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M45" s="4"/>
+      <c r="N45" s="5"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -1653,12 +1866,13 @@
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
-      <c r="L46" s="9"/>
-      <c r="M46" s="5"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Input_Data_Sheets/SOIL_parameters.xlsx
+++ b/Input_Data_Sheets/SOIL_parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mngomes/Documents/GitHub/HydroPol2D/Input_Data_Sheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mngomes/Documents/Pune/HydroPol2D/Input_Data_Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD6D3D9-5A2C-2D44-9695-A9648FBBFEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2625F404-FEA6-BD49-BD67-49026C7D7187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1179,7 +1179,8 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="H3" s="7">
-        <v>0.2</v>
+        <f>(F3-G3)*0.1+G3</f>
+        <v>9.9700000000000011E-2</v>
       </c>
       <c r="I3" s="7">
         <v>0.03</v>
@@ -1216,7 +1217,8 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="H4" s="7">
-        <v>0.22</v>
+        <f t="shared" ref="H4:H15" si="0">(F4-G4)*0.1+G4</f>
+        <v>0.12239999999999999</v>
       </c>
       <c r="I4" s="7">
         <v>0.04</v>
@@ -1253,7 +1255,8 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="H5" s="7">
-        <v>0.17</v>
+        <f t="shared" si="0"/>
+        <v>9.9599999999999994E-2</v>
       </c>
       <c r="I5" s="7">
         <v>0.06</v>
@@ -1290,7 +1293,8 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="H6" s="7">
-        <v>0.16</v>
+        <f t="shared" si="0"/>
+        <v>0.1164</v>
       </c>
       <c r="I6" s="7">
         <v>0.08</v>
@@ -1327,7 +1331,8 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="H7" s="7">
-        <v>0.22</v>
+        <f t="shared" si="0"/>
+        <v>0.12329999999999999</v>
       </c>
       <c r="I7" s="7">
         <v>0.09</v>
@@ -1364,7 +1369,8 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="H8" s="7">
-        <v>0.17</v>
+        <f t="shared" si="0"/>
+        <v>9.1499999999999998E-2</v>
       </c>
       <c r="I8" s="7">
         <v>0.11</v>
@@ -1401,7 +1407,8 @@
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="H9" s="7">
-        <v>0.22</v>
+        <f t="shared" si="0"/>
+        <v>0.10370000000000001</v>
       </c>
       <c r="I9" s="7">
         <v>0.14000000000000001</v>
@@ -1438,7 +1445,8 @@
         <v>7.8E-2</v>
       </c>
       <c r="H10" s="7">
-        <v>0.25</v>
+        <f t="shared" si="0"/>
+        <v>0.1188</v>
       </c>
       <c r="I10" s="7">
         <v>0.18</v>
@@ -1475,7 +1483,8 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="H11" s="7">
-        <v>0.21</v>
+        <f t="shared" si="0"/>
+        <v>9.9700000000000011E-2</v>
       </c>
       <c r="I11" s="7">
         <v>0.22</v>
@@ -1512,7 +1521,8 @@
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="H12" s="7">
-        <v>0.24</v>
+        <f t="shared" si="0"/>
+        <v>0.1089</v>
       </c>
       <c r="I12" s="7">
         <v>0.12</v>
@@ -1549,7 +1559,8 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="H13" s="7">
-        <v>0.2</v>
+        <f t="shared" si="0"/>
+        <v>9.1400000000000009E-2</v>
       </c>
       <c r="I13" s="7">
         <v>0.25</v>
@@ -1586,7 +1597,8 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="H14" s="7">
-        <v>0.21</v>
+        <f t="shared" si="0"/>
+        <v>8.2199999999999995E-2</v>
       </c>
       <c r="I14" s="7">
         <v>0.3</v>
@@ -1623,7 +1635,8 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="H15" s="7">
-        <v>0.2</v>
+        <f t="shared" si="0"/>
+        <v>9.9700000000000011E-2</v>
       </c>
       <c r="I15" s="7">
         <v>0.03</v>

--- a/Input_Data_Sheets/SOIL_parameters.xlsx
+++ b/Input_Data_Sheets/SOIL_parameters.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -81,8 +81,53 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -101,8 +146,28 @@
         <bgColor theme="0" tint="-0.0499893185216834"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -150,11 +215,68 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+    </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="dashed">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="dashed">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -183,6 +305,42 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,993 +741,1695 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="17.5" customWidth="1" style="1" min="1" max="1"/>
-    <col width="12.5" customWidth="1" style="1" min="2" max="2"/>
-    <col width="21.6640625" customWidth="1" style="1" min="3" max="3"/>
-    <col width="8.83203125" customWidth="1" style="1" min="4" max="5"/>
-    <col width="16.33203125" customWidth="1" style="1" min="6" max="6"/>
-    <col width="19.1640625" customWidth="1" style="1" min="7" max="12"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" style="1" min="13" max="14"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="8.83203125" customWidth="1" style="1" min="15" max="16384"/>
+    <col width="26" customWidth="1" style="1" min="1" max="1"/>
+    <col width="12" customWidth="1" style="1" min="2" max="2"/>
+    <col width="14" customWidth="1" style="1" min="3" max="3"/>
+    <col width="12" customWidth="1" style="1" min="4" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" style="1" min="6" max="6"/>
+    <col width="16" customWidth="1" style="1" min="7" max="12"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" style="1" min="13" max="14"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" style="1" min="15" max="16384"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" thickBot="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>HydroPol2D - Soil Parameters</t>
-        </is>
-      </c>
-      <c r="M1" s="13" t="n"/>
-      <c r="P1" s="13" t="n"/>
-      <c r="Q1" s="11" t="n"/>
-    </row>
-    <row r="2" ht="21" customHeight="1" thickBot="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" thickBot="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>HydroPol2D Model - Soil Parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1" thickBot="1">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Soil_type</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="22" t="inlineStr">
         <is>
           <t>ksat (mm/h)</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>n [-]</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="22" t="inlineStr">
         <is>
           <t>alpha [1/m]</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr">
         <is>
           <t>θsat (cm3.cm-3)</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="22" t="inlineStr">
         <is>
           <t>θr (cm3.cm-3)</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>θi (cm3.cm-3)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="22" t="inlineStr">
         <is>
           <t>Sy [-]</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="22" t="inlineStr">
         <is>
           <t>kgsat (mm/h)</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="22" t="inlineStr">
         <is>
           <t>DTB (m)</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="22" t="inlineStr">
         <is>
           <t>Ks_multiplier_near_surface</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="22" t="inlineStr">
         <is>
           <t>Ks_multiplier_root_zone</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="22" t="inlineStr">
         <is>
           <t>Ks_multiplier_transmission</t>
         </is>
       </c>
-      <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="O2" s="22" t="inlineStr">
+        <is>
+          <t>Ltop_m</t>
+        </is>
+      </c>
+      <c r="P2" s="22" t="inlineStr">
+        <is>
+          <t>dh_max_m</t>
+        </is>
+      </c>
+      <c r="Q2" s="22" t="inlineStr">
+        <is>
+          <t>l_vg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Clay</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="n">
+      <c r="B3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="24" t="n">
         <v>0.3</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="24" t="n">
         <v>1.09</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E3" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="24" t="n">
         <v>0.385</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="24" t="n">
         <v>0.068</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="24" t="n">
         <v>0.0997</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="J3" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="K3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="K3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Silty Clay</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="24" t="n">
         <v>1.23</v>
       </c>
-      <c r="E4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7" t="n">
+      <c r="E4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="24" t="n">
         <v>0.423</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="24" t="n">
         <v>0.089</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="24" t="n">
         <v>0.1224</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="24" t="n">
         <v>0.04</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="J4" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="K4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="K4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Sandy Clay</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="24" t="n">
         <v>0.6</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="24" t="n">
         <v>1.31</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="24" t="n">
         <v>0.321</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="24" t="n">
         <v>0.075</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="24" t="n">
         <v>0.09959999999999999</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="24" t="n">
         <v>0.06</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="J5" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="K5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="K5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Clay Loam</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7" t="n">
+      <c r="C6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="24" t="n">
         <v>1.31</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="24" t="n">
         <v>1.9</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="24" t="n">
         <v>0.309</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="24" t="n">
         <v>0.095</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="24" t="n">
         <v>0.1164</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="24" t="n">
         <v>0.08</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J6" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="K6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="K6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Silty Clay Loam</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7" t="n">
+      <c r="C7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="24" t="n">
         <v>1.23</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="24" t="n">
         <v>0.432</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="24" t="n">
         <v>0.089</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="24" t="n">
         <v>0.1233</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="24" t="n">
         <v>0.09</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="J7" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="K7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="K7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Sandy Clay Loam</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="24" t="n">
         <v>1.48</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="24" t="n">
         <v>0.33</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="24" t="n">
         <v>0.065</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="24" t="n">
         <v>0.0915</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="24" t="n">
         <v>0.11</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="J8" s="24" t="n">
         <v>30</v>
       </c>
-      <c r="K8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="K8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Silty Loam</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="24" t="n">
         <v>7.6</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="24" t="n">
         <v>1.41</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="24" t="n">
         <v>4.5</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="24" t="n">
         <v>0.434</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="24" t="n">
         <v>0.067</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="24" t="n">
         <v>0.122</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="24" t="n">
         <v>0.14</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="J9" s="24" t="n">
         <v>152</v>
       </c>
-      <c r="K9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="K9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Loam</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="24" t="n">
         <v>3.4</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="24" t="n">
         <v>1.56</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="24" t="n">
         <v>3.6</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="24" t="n">
         <v>0.486</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="24" t="n">
         <v>0.078</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="24" t="n">
         <v>0.1104</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="24" t="n">
         <v>0.18</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J10" s="24" t="n">
         <v>68</v>
       </c>
-      <c r="K10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="K10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>Sandy Loam</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="24" t="n">
         <v>10.9</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="24" t="n">
         <v>1.89</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="24" t="n">
         <v>7.5</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="24" t="n">
         <v>0.412</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="24" t="n">
         <v>0.065</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="24" t="n">
         <v>0.1287</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="24" t="n">
         <v>0.22</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="24" t="n">
         <v>218</v>
       </c>
-      <c r="K11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="4" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="K11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>Silt</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="24" t="n">
         <v>3.4</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="24" t="n">
         <v>1.37</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="24" t="n">
         <v>0.486</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="24" t="n">
         <v>0.067</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="24" t="n">
         <v>0.1234</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="24" t="n">
         <v>0.12</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="24" t="n">
         <v>68</v>
       </c>
-      <c r="K12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="K12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>Loamy Sand</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="24" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="24" t="n">
         <v>29.9</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="24" t="n">
         <v>2.28</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="24" t="n">
         <v>14.5</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="24" t="n">
         <v>0.401</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="24" t="n">
         <v>0.057</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="24" t="n">
         <v>0.1172</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="24" t="n">
         <v>0.25</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="J13" s="24" t="n">
         <v>598</v>
       </c>
-      <c r="K13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="K13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Sand</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="24" t="n">
         <v>117.8</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="24" t="n">
         <v>2.68</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="24" t="n">
         <v>14.5</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="24" t="n">
         <v>0.417</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="24" t="n">
         <v>0.045</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="24" t="n">
         <v>0.1225</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="24" t="n">
         <v>0.3</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J14" s="24" t="n">
         <v>2356</v>
       </c>
-      <c r="K14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" s="4" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="K14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>Water</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="24" t="n">
         <v>0.3</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="24" t="n">
         <v>1.09</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="24" t="n">
         <v>0.385</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="24" t="n">
         <v>0.068</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="24" t="n">
         <v>0.0997</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="J15" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="K15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="4" t="n"/>
-      <c r="Q15" s="5" t="n"/>
+      <c r="K15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="24" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="5" t="n"/>
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="25" t="n"/>
+      <c r="M16" s="25" t="n"/>
+      <c r="N16" s="25" t="n"/>
+      <c r="O16" s="25" t="n"/>
+      <c r="P16" s="25" t="n"/>
+      <c r="Q16" s="25" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="4" t="n"/>
-      <c r="Q17" s="5" t="n"/>
+      <c r="A17" s="25" t="n"/>
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="25" t="n"/>
+      <c r="L17" s="25" t="n"/>
+      <c r="M17" s="25" t="n"/>
+      <c r="N17" s="25" t="n"/>
+      <c r="O17" s="25" t="n"/>
+      <c r="P17" s="25" t="n"/>
+      <c r="Q17" s="25" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="7" t="n"/>
-      <c r="N18" s="7" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="5" t="n"/>
+      <c r="A18" s="25" t="n"/>
+      <c r="B18" s="25" t="n"/>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="25" t="n"/>
+      <c r="L18" s="25" t="n"/>
+      <c r="M18" s="25" t="n"/>
+      <c r="N18" s="25" t="n"/>
+      <c r="O18" s="25" t="n"/>
+      <c r="P18" s="25" t="n"/>
+      <c r="Q18" s="25" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="5" t="n"/>
+      <c r="A19" s="25" t="n"/>
+      <c r="B19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="25" t="n"/>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="25" t="n"/>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="25" t="n"/>
+      <c r="L19" s="25" t="n"/>
+      <c r="M19" s="25" t="n"/>
+      <c r="N19" s="25" t="n"/>
+      <c r="O19" s="25" t="n"/>
+      <c r="P19" s="25" t="n"/>
+      <c r="Q19" s="25" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
-      <c r="N20" s="7" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="4" t="n"/>
-      <c r="Q20" s="5" t="n"/>
+      <c r="A20" s="25" t="n"/>
+      <c r="B20" s="25" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="25" t="n"/>
+      <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="25" t="n"/>
+      <c r="L20" s="25" t="n"/>
+      <c r="M20" s="25" t="n"/>
+      <c r="N20" s="25" t="n"/>
+      <c r="O20" s="25" t="n"/>
+      <c r="P20" s="25" t="n"/>
+      <c r="Q20" s="25" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="4" t="n"/>
-      <c r="Q21" s="5" t="n"/>
+      <c r="A21" s="25" t="n"/>
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
+      <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="25" t="n"/>
+      <c r="L21" s="25" t="n"/>
+      <c r="M21" s="25" t="n"/>
+      <c r="N21" s="25" t="n"/>
+      <c r="O21" s="25" t="n"/>
+      <c r="P21" s="25" t="n"/>
+      <c r="Q21" s="25" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="4" t="n"/>
-      <c r="Q22" s="5" t="n"/>
+      <c r="A22" s="25" t="n"/>
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="25" t="n"/>
+      <c r="L22" s="25" t="n"/>
+      <c r="M22" s="25" t="n"/>
+      <c r="N22" s="25" t="n"/>
+      <c r="O22" s="25" t="n"/>
+      <c r="P22" s="25" t="n"/>
+      <c r="Q22" s="25" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="6" t="n"/>
-      <c r="P23" s="4" t="n"/>
-      <c r="Q23" s="5" t="n"/>
+      <c r="A23" s="25" t="n"/>
+      <c r="B23" s="25" t="n"/>
+      <c r="C23" s="25" t="n"/>
+      <c r="D23" s="25" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="25" t="n"/>
+      <c r="L23" s="25" t="n"/>
+      <c r="M23" s="25" t="n"/>
+      <c r="N23" s="25" t="n"/>
+      <c r="O23" s="25" t="n"/>
+      <c r="P23" s="25" t="n"/>
+      <c r="Q23" s="25" t="n"/>
     </row>
     <row r="24">
-      <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="5" t="n"/>
+      <c r="A24" s="25" t="n"/>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="25" t="n"/>
+      <c r="L24" s="25" t="n"/>
+      <c r="M24" s="25" t="n"/>
+      <c r="N24" s="25" t="n"/>
+      <c r="O24" s="25" t="n"/>
+      <c r="P24" s="25" t="n"/>
+      <c r="Q24" s="25" t="n"/>
     </row>
     <row r="25">
-      <c r="P25" s="4" t="n"/>
-      <c r="Q25" s="5" t="n"/>
+      <c r="A25" s="25" t="n"/>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="25" t="n"/>
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="25" t="n"/>
+      <c r="G25" s="25" t="n"/>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="25" t="n"/>
+      <c r="L25" s="25" t="n"/>
+      <c r="M25" s="25" t="n"/>
+      <c r="N25" s="25" t="n"/>
+      <c r="O25" s="25" t="n"/>
+      <c r="P25" s="25" t="n"/>
+      <c r="Q25" s="25" t="n"/>
     </row>
     <row r="26">
-      <c r="P26" s="4" t="n"/>
-      <c r="Q26" s="5" t="n"/>
+      <c r="A26" s="25" t="n"/>
+      <c r="B26" s="25" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="25" t="n"/>
+      <c r="G26" s="25" t="n"/>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="25" t="n"/>
+      <c r="L26" s="25" t="n"/>
+      <c r="M26" s="25" t="n"/>
+      <c r="N26" s="25" t="n"/>
+      <c r="O26" s="25" t="n"/>
+      <c r="P26" s="25" t="n"/>
+      <c r="Q26" s="25" t="n"/>
     </row>
     <row r="27">
-      <c r="P27" s="4" t="n"/>
-      <c r="Q27" s="5" t="n"/>
+      <c r="A27" s="25" t="n"/>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="25" t="n"/>
+      <c r="D27" s="25" t="n"/>
+      <c r="E27" s="25" t="n"/>
+      <c r="F27" s="25" t="n"/>
+      <c r="G27" s="25" t="n"/>
+      <c r="H27" s="25" t="n"/>
+      <c r="I27" s="25" t="n"/>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="25" t="n"/>
+      <c r="L27" s="25" t="n"/>
+      <c r="M27" s="25" t="n"/>
+      <c r="N27" s="25" t="n"/>
+      <c r="O27" s="25" t="n"/>
+      <c r="P27" s="25" t="n"/>
+      <c r="Q27" s="25" t="n"/>
     </row>
     <row r="28">
-      <c r="P28" s="4" t="n"/>
-      <c r="Q28" s="5" t="n"/>
+      <c r="A28" s="25" t="n"/>
+      <c r="B28" s="25" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="25" t="n"/>
+      <c r="L28" s="25" t="n"/>
+      <c r="M28" s="25" t="n"/>
+      <c r="N28" s="25" t="n"/>
+      <c r="O28" s="25" t="n"/>
+      <c r="P28" s="25" t="n"/>
+      <c r="Q28" s="25" t="n"/>
     </row>
     <row r="29">
-      <c r="P29" s="4" t="n"/>
-      <c r="Q29" s="5" t="n"/>
+      <c r="A29" s="25" t="n"/>
+      <c r="B29" s="25" t="n"/>
+      <c r="C29" s="25" t="n"/>
+      <c r="D29" s="25" t="n"/>
+      <c r="E29" s="25" t="n"/>
+      <c r="F29" s="25" t="n"/>
+      <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
+      <c r="I29" s="25" t="n"/>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="25" t="n"/>
+      <c r="L29" s="25" t="n"/>
+      <c r="M29" s="25" t="n"/>
+      <c r="N29" s="25" t="n"/>
+      <c r="O29" s="25" t="n"/>
+      <c r="P29" s="25" t="n"/>
+      <c r="Q29" s="25" t="n"/>
     </row>
     <row r="30">
-      <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="5" t="n"/>
+      <c r="A30" s="25" t="n"/>
+      <c r="B30" s="25" t="n"/>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="25" t="n"/>
+      <c r="L30" s="25" t="n"/>
+      <c r="M30" s="25" t="n"/>
+      <c r="N30" s="25" t="n"/>
+      <c r="O30" s="25" t="n"/>
+      <c r="P30" s="25" t="n"/>
+      <c r="Q30" s="25" t="n"/>
     </row>
     <row r="31">
-      <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="5" t="n"/>
+      <c r="A31" s="25" t="n"/>
+      <c r="B31" s="25" t="n"/>
+      <c r="C31" s="25" t="n"/>
+      <c r="D31" s="25" t="n"/>
+      <c r="E31" s="25" t="n"/>
+      <c r="F31" s="25" t="n"/>
+      <c r="G31" s="25" t="n"/>
+      <c r="H31" s="25" t="n"/>
+      <c r="I31" s="25" t="n"/>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="25" t="n"/>
+      <c r="L31" s="25" t="n"/>
+      <c r="M31" s="25" t="n"/>
+      <c r="N31" s="25" t="n"/>
+      <c r="O31" s="25" t="n"/>
+      <c r="P31" s="25" t="n"/>
+      <c r="Q31" s="25" t="n"/>
     </row>
     <row r="32">
-      <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="5" t="n"/>
+      <c r="A32" s="25" t="n"/>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="25" t="n"/>
+      <c r="D32" s="25" t="n"/>
+      <c r="E32" s="25" t="n"/>
+      <c r="F32" s="25" t="n"/>
+      <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="25" t="n"/>
+      <c r="L32" s="25" t="n"/>
+      <c r="M32" s="25" t="n"/>
+      <c r="N32" s="25" t="n"/>
+      <c r="O32" s="25" t="n"/>
+      <c r="P32" s="25" t="n"/>
+      <c r="Q32" s="25" t="n"/>
     </row>
     <row r="33">
-      <c r="P33" s="4" t="n"/>
-      <c r="Q33" s="5" t="n"/>
+      <c r="A33" s="25" t="n"/>
+      <c r="B33" s="25" t="n"/>
+      <c r="C33" s="25" t="n"/>
+      <c r="D33" s="25" t="n"/>
+      <c r="E33" s="25" t="n"/>
+      <c r="F33" s="25" t="n"/>
+      <c r="G33" s="25" t="n"/>
+      <c r="H33" s="25" t="n"/>
+      <c r="I33" s="25" t="n"/>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="25" t="n"/>
+      <c r="L33" s="25" t="n"/>
+      <c r="M33" s="25" t="n"/>
+      <c r="N33" s="25" t="n"/>
+      <c r="O33" s="25" t="n"/>
+      <c r="P33" s="25" t="n"/>
+      <c r="Q33" s="25" t="n"/>
     </row>
     <row r="34">
-      <c r="P34" s="4" t="n"/>
-      <c r="Q34" s="5" t="n"/>
+      <c r="A34" s="25" t="n"/>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="25" t="n"/>
+      <c r="D34" s="25" t="n"/>
+      <c r="E34" s="25" t="n"/>
+      <c r="F34" s="25" t="n"/>
+      <c r="G34" s="25" t="n"/>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="25" t="n"/>
+      <c r="L34" s="25" t="n"/>
+      <c r="M34" s="25" t="n"/>
+      <c r="N34" s="25" t="n"/>
+      <c r="O34" s="25" t="n"/>
+      <c r="P34" s="25" t="n"/>
+      <c r="Q34" s="25" t="n"/>
     </row>
     <row r="35">
-      <c r="P35" s="4" t="n"/>
-      <c r="Q35" s="5" t="n"/>
+      <c r="A35" s="25" t="n"/>
+      <c r="B35" s="25" t="n"/>
+      <c r="C35" s="25" t="n"/>
+      <c r="D35" s="25" t="n"/>
+      <c r="E35" s="25" t="n"/>
+      <c r="F35" s="25" t="n"/>
+      <c r="G35" s="25" t="n"/>
+      <c r="H35" s="25" t="n"/>
+      <c r="I35" s="25" t="n"/>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="25" t="n"/>
+      <c r="L35" s="25" t="n"/>
+      <c r="M35" s="25" t="n"/>
+      <c r="N35" s="25" t="n"/>
+      <c r="O35" s="25" t="n"/>
+      <c r="P35" s="25" t="n"/>
+      <c r="Q35" s="25" t="n"/>
     </row>
     <row r="36">
-      <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="5" t="n"/>
+      <c r="A36" s="25" t="n"/>
+      <c r="B36" s="25" t="n"/>
+      <c r="C36" s="25" t="n"/>
+      <c r="D36" s="25" t="n"/>
+      <c r="E36" s="25" t="n"/>
+      <c r="F36" s="25" t="n"/>
+      <c r="G36" s="25" t="n"/>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="25" t="n"/>
+      <c r="L36" s="25" t="n"/>
+      <c r="M36" s="25" t="n"/>
+      <c r="N36" s="25" t="n"/>
+      <c r="O36" s="25" t="n"/>
+      <c r="P36" s="25" t="n"/>
+      <c r="Q36" s="25" t="n"/>
     </row>
     <row r="37">
-      <c r="P37" s="4" t="n"/>
-      <c r="Q37" s="5" t="n"/>
+      <c r="A37" s="25" t="n"/>
+      <c r="B37" s="25" t="n"/>
+      <c r="C37" s="25" t="n"/>
+      <c r="D37" s="25" t="n"/>
+      <c r="E37" s="25" t="n"/>
+      <c r="F37" s="25" t="n"/>
+      <c r="G37" s="25" t="n"/>
+      <c r="H37" s="25" t="n"/>
+      <c r="I37" s="25" t="n"/>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="25" t="n"/>
+      <c r="L37" s="25" t="n"/>
+      <c r="M37" s="25" t="n"/>
+      <c r="N37" s="25" t="n"/>
+      <c r="O37" s="25" t="n"/>
+      <c r="P37" s="25" t="n"/>
+      <c r="Q37" s="25" t="n"/>
     </row>
     <row r="38">
-      <c r="P38" s="4" t="n"/>
-      <c r="Q38" s="5" t="n"/>
+      <c r="A38" s="25" t="n"/>
+      <c r="B38" s="25" t="n"/>
+      <c r="C38" s="25" t="n"/>
+      <c r="D38" s="25" t="n"/>
+      <c r="E38" s="25" t="n"/>
+      <c r="F38" s="25" t="n"/>
+      <c r="G38" s="25" t="n"/>
+      <c r="H38" s="25" t="n"/>
+      <c r="I38" s="25" t="n"/>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="25" t="n"/>
+      <c r="L38" s="25" t="n"/>
+      <c r="M38" s="25" t="n"/>
+      <c r="N38" s="25" t="n"/>
+      <c r="O38" s="25" t="n"/>
+      <c r="P38" s="25" t="n"/>
+      <c r="Q38" s="25" t="n"/>
     </row>
     <row r="39">
-      <c r="P39" s="4" t="n"/>
-      <c r="Q39" s="5" t="n"/>
+      <c r="A39" s="25" t="n"/>
+      <c r="B39" s="25" t="n"/>
+      <c r="C39" s="25" t="n"/>
+      <c r="D39" s="25" t="n"/>
+      <c r="E39" s="25" t="n"/>
+      <c r="F39" s="25" t="n"/>
+      <c r="G39" s="25" t="n"/>
+      <c r="H39" s="25" t="n"/>
+      <c r="I39" s="25" t="n"/>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="25" t="n"/>
+      <c r="L39" s="25" t="n"/>
+      <c r="M39" s="25" t="n"/>
+      <c r="N39" s="25" t="n"/>
+      <c r="O39" s="25" t="n"/>
+      <c r="P39" s="25" t="n"/>
+      <c r="Q39" s="25" t="n"/>
     </row>
     <row r="40">
-      <c r="P40" s="4" t="n"/>
-      <c r="Q40" s="5" t="n"/>
+      <c r="A40" s="25" t="n"/>
+      <c r="B40" s="25" t="n"/>
+      <c r="C40" s="25" t="n"/>
+      <c r="D40" s="25" t="n"/>
+      <c r="E40" s="25" t="n"/>
+      <c r="F40" s="25" t="n"/>
+      <c r="G40" s="25" t="n"/>
+      <c r="H40" s="25" t="n"/>
+      <c r="I40" s="25" t="n"/>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="25" t="n"/>
+      <c r="L40" s="25" t="n"/>
+      <c r="M40" s="25" t="n"/>
+      <c r="N40" s="25" t="n"/>
+      <c r="O40" s="25" t="n"/>
+      <c r="P40" s="25" t="n"/>
+      <c r="Q40" s="25" t="n"/>
     </row>
     <row r="41">
-      <c r="P41" s="4" t="n"/>
-      <c r="Q41" s="5" t="n"/>
+      <c r="A41" s="25" t="n"/>
+      <c r="B41" s="25" t="n"/>
+      <c r="C41" s="25" t="n"/>
+      <c r="D41" s="25" t="n"/>
+      <c r="E41" s="25" t="n"/>
+      <c r="F41" s="25" t="n"/>
+      <c r="G41" s="25" t="n"/>
+      <c r="H41" s="25" t="n"/>
+      <c r="I41" s="25" t="n"/>
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="25" t="n"/>
+      <c r="L41" s="25" t="n"/>
+      <c r="M41" s="25" t="n"/>
+      <c r="N41" s="25" t="n"/>
+      <c r="O41" s="25" t="n"/>
+      <c r="P41" s="25" t="n"/>
+      <c r="Q41" s="25" t="n"/>
     </row>
     <row r="42">
-      <c r="P42" s="4" t="n"/>
-      <c r="Q42" s="5" t="n"/>
+      <c r="A42" s="25" t="n"/>
+      <c r="B42" s="25" t="n"/>
+      <c r="C42" s="25" t="n"/>
+      <c r="D42" s="25" t="n"/>
+      <c r="E42" s="25" t="n"/>
+      <c r="F42" s="25" t="n"/>
+      <c r="G42" s="25" t="n"/>
+      <c r="H42" s="25" t="n"/>
+      <c r="I42" s="25" t="n"/>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="25" t="n"/>
+      <c r="L42" s="25" t="n"/>
+      <c r="M42" s="25" t="n"/>
+      <c r="N42" s="25" t="n"/>
+      <c r="O42" s="25" t="n"/>
+      <c r="P42" s="25" t="n"/>
+      <c r="Q42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="P43" s="4" t="n"/>
-      <c r="Q43" s="5" t="n"/>
+      <c r="A43" s="25" t="n"/>
+      <c r="B43" s="25" t="n"/>
+      <c r="C43" s="25" t="n"/>
+      <c r="D43" s="25" t="n"/>
+      <c r="E43" s="25" t="n"/>
+      <c r="F43" s="25" t="n"/>
+      <c r="G43" s="25" t="n"/>
+      <c r="H43" s="25" t="n"/>
+      <c r="I43" s="25" t="n"/>
+      <c r="J43" s="25" t="n"/>
+      <c r="K43" s="25" t="n"/>
+      <c r="L43" s="25" t="n"/>
+      <c r="M43" s="25" t="n"/>
+      <c r="N43" s="25" t="n"/>
+      <c r="O43" s="25" t="n"/>
+      <c r="P43" s="25" t="n"/>
+      <c r="Q43" s="25" t="n"/>
     </row>
     <row r="44">
-      <c r="P44" s="4" t="n"/>
-      <c r="Q44" s="5" t="n"/>
+      <c r="A44" s="25" t="n"/>
+      <c r="B44" s="25" t="n"/>
+      <c r="C44" s="25" t="n"/>
+      <c r="D44" s="25" t="n"/>
+      <c r="E44" s="25" t="n"/>
+      <c r="F44" s="25" t="n"/>
+      <c r="G44" s="25" t="n"/>
+      <c r="H44" s="25" t="n"/>
+      <c r="I44" s="25" t="n"/>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="25" t="n"/>
+      <c r="L44" s="25" t="n"/>
+      <c r="M44" s="25" t="n"/>
+      <c r="N44" s="25" t="n"/>
+      <c r="O44" s="25" t="n"/>
+      <c r="P44" s="25" t="n"/>
+      <c r="Q44" s="25" t="n"/>
     </row>
     <row r="45">
-      <c r="P45" s="4" t="n"/>
-      <c r="Q45" s="5" t="n"/>
+      <c r="A45" s="25" t="n"/>
+      <c r="B45" s="25" t="n"/>
+      <c r="C45" s="25" t="n"/>
+      <c r="D45" s="25" t="n"/>
+      <c r="E45" s="25" t="n"/>
+      <c r="F45" s="25" t="n"/>
+      <c r="G45" s="25" t="n"/>
+      <c r="H45" s="25" t="n"/>
+      <c r="I45" s="25" t="n"/>
+      <c r="J45" s="25" t="n"/>
+      <c r="K45" s="25" t="n"/>
+      <c r="L45" s="25" t="n"/>
+      <c r="M45" s="25" t="n"/>
+      <c r="N45" s="25" t="n"/>
+      <c r="O45" s="25" t="n"/>
+      <c r="P45" s="25" t="n"/>
+      <c r="Q45" s="25" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="n"/>
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="8" t="n"/>
-      <c r="J46" s="8" t="n"/>
-      <c r="K46" s="8" t="n"/>
-      <c r="L46" s="8" t="n"/>
-      <c r="M46" s="8" t="n"/>
-      <c r="N46" s="8" t="n"/>
-      <c r="O46" s="8" t="n"/>
-      <c r="P46" s="9" t="n"/>
-      <c r="Q46" s="5" t="n"/>
+      <c r="A46" s="25" t="n"/>
+      <c r="B46" s="25" t="n"/>
+      <c r="C46" s="25" t="n"/>
+      <c r="D46" s="25" t="n"/>
+      <c r="E46" s="25" t="n"/>
+      <c r="F46" s="25" t="n"/>
+      <c r="G46" s="25" t="n"/>
+      <c r="H46" s="25" t="n"/>
+      <c r="I46" s="25" t="n"/>
+      <c r="J46" s="25" t="n"/>
+      <c r="K46" s="25" t="n"/>
+      <c r="L46" s="25" t="n"/>
+      <c r="M46" s="25" t="n"/>
+      <c r="N46" s="25" t="n"/>
+      <c r="O46" s="25" t="n"/>
+      <c r="P46" s="25" t="n"/>
+      <c r="Q46" s="25" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="n"/>
+      <c r="B47" s="25" t="n"/>
+      <c r="C47" s="25" t="n"/>
+      <c r="D47" s="25" t="n"/>
+      <c r="E47" s="25" t="n"/>
+      <c r="F47" s="25" t="n"/>
+      <c r="G47" s="25" t="n"/>
+      <c r="H47" s="25" t="n"/>
+      <c r="I47" s="25" t="n"/>
+      <c r="J47" s="25" t="n"/>
+      <c r="K47" s="25" t="n"/>
+      <c r="L47" s="25" t="n"/>
+      <c r="M47" s="25" t="n"/>
+      <c r="N47" s="25" t="n"/>
+      <c r="O47" s="25" t="n"/>
+      <c r="P47" s="25" t="n"/>
+      <c r="Q47" s="25" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="n"/>
+      <c r="B48" s="25" t="n"/>
+      <c r="C48" s="25" t="n"/>
+      <c r="D48" s="25" t="n"/>
+      <c r="E48" s="25" t="n"/>
+      <c r="F48" s="25" t="n"/>
+      <c r="G48" s="25" t="n"/>
+      <c r="H48" s="25" t="n"/>
+      <c r="I48" s="25" t="n"/>
+      <c r="J48" s="25" t="n"/>
+      <c r="K48" s="25" t="n"/>
+      <c r="L48" s="25" t="n"/>
+      <c r="M48" s="25" t="n"/>
+      <c r="N48" s="25" t="n"/>
+      <c r="O48" s="25" t="n"/>
+      <c r="P48" s="25" t="n"/>
+      <c r="Q48" s="25" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="25" t="n"/>
+      <c r="B49" s="25" t="n"/>
+      <c r="C49" s="25" t="n"/>
+      <c r="D49" s="25" t="n"/>
+      <c r="E49" s="25" t="n"/>
+      <c r="F49" s="25" t="n"/>
+      <c r="G49" s="25" t="n"/>
+      <c r="H49" s="25" t="n"/>
+      <c r="I49" s="25" t="n"/>
+      <c r="J49" s="25" t="n"/>
+      <c r="K49" s="25" t="n"/>
+      <c r="L49" s="25" t="n"/>
+      <c r="M49" s="25" t="n"/>
+      <c r="N49" s="25" t="n"/>
+      <c r="O49" s="25" t="n"/>
+      <c r="P49" s="25" t="n"/>
+      <c r="Q49" s="25" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="n"/>
+      <c r="B50" s="25" t="n"/>
+      <c r="C50" s="25" t="n"/>
+      <c r="D50" s="25" t="n"/>
+      <c r="E50" s="25" t="n"/>
+      <c r="F50" s="25" t="n"/>
+      <c r="G50" s="25" t="n"/>
+      <c r="H50" s="25" t="n"/>
+      <c r="I50" s="25" t="n"/>
+      <c r="J50" s="25" t="n"/>
+      <c r="K50" s="25" t="n"/>
+      <c r="L50" s="25" t="n"/>
+      <c r="M50" s="25" t="n"/>
+      <c r="N50" s="25" t="n"/>
+      <c r="O50" s="25" t="n"/>
+      <c r="P50" s="25" t="n"/>
+      <c r="Q50" s="25" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="25" t="n"/>
+      <c r="B51" s="25" t="n"/>
+      <c r="C51" s="25" t="n"/>
+      <c r="D51" s="25" t="n"/>
+      <c r="E51" s="25" t="n"/>
+      <c r="F51" s="25" t="n"/>
+      <c r="G51" s="25" t="n"/>
+      <c r="H51" s="25" t="n"/>
+      <c r="I51" s="25" t="n"/>
+      <c r="J51" s="25" t="n"/>
+      <c r="K51" s="25" t="n"/>
+      <c r="L51" s="25" t="n"/>
+      <c r="M51" s="25" t="n"/>
+      <c r="N51" s="25" t="n"/>
+      <c r="O51" s="25" t="n"/>
+      <c r="P51" s="25" t="n"/>
+      <c r="Q51" s="25" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="n"/>
+      <c r="B52" s="25" t="n"/>
+      <c r="C52" s="25" t="n"/>
+      <c r="D52" s="25" t="n"/>
+      <c r="E52" s="25" t="n"/>
+      <c r="F52" s="25" t="n"/>
+      <c r="G52" s="25" t="n"/>
+      <c r="H52" s="25" t="n"/>
+      <c r="I52" s="25" t="n"/>
+      <c r="J52" s="25" t="n"/>
+      <c r="K52" s="25" t="n"/>
+      <c r="L52" s="25" t="n"/>
+      <c r="M52" s="25" t="n"/>
+      <c r="N52" s="25" t="n"/>
+      <c r="O52" s="25" t="n"/>
+      <c r="P52" s="25" t="n"/>
+      <c r="Q52" s="25" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="n"/>
+      <c r="B53" s="25" t="n"/>
+      <c r="C53" s="25" t="n"/>
+      <c r="D53" s="25" t="n"/>
+      <c r="E53" s="25" t="n"/>
+      <c r="F53" s="25" t="n"/>
+      <c r="G53" s="25" t="n"/>
+      <c r="H53" s="25" t="n"/>
+      <c r="I53" s="25" t="n"/>
+      <c r="J53" s="25" t="n"/>
+      <c r="K53" s="25" t="n"/>
+      <c r="L53" s="25" t="n"/>
+      <c r="M53" s="25" t="n"/>
+      <c r="N53" s="25" t="n"/>
+      <c r="O53" s="25" t="n"/>
+      <c r="P53" s="25" t="n"/>
+      <c r="Q53" s="25" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="n"/>
+      <c r="B54" s="25" t="n"/>
+      <c r="C54" s="25" t="n"/>
+      <c r="D54" s="25" t="n"/>
+      <c r="E54" s="25" t="n"/>
+      <c r="F54" s="25" t="n"/>
+      <c r="G54" s="25" t="n"/>
+      <c r="H54" s="25" t="n"/>
+      <c r="I54" s="25" t="n"/>
+      <c r="J54" s="25" t="n"/>
+      <c r="K54" s="25" t="n"/>
+      <c r="L54" s="25" t="n"/>
+      <c r="M54" s="25" t="n"/>
+      <c r="N54" s="25" t="n"/>
+      <c r="O54" s="25" t="n"/>
+      <c r="P54" s="25" t="n"/>
+      <c r="Q54" s="25" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="25" t="n"/>
+      <c r="B55" s="25" t="n"/>
+      <c r="C55" s="25" t="n"/>
+      <c r="D55" s="25" t="n"/>
+      <c r="E55" s="25" t="n"/>
+      <c r="F55" s="25" t="n"/>
+      <c r="G55" s="25" t="n"/>
+      <c r="H55" s="25" t="n"/>
+      <c r="I55" s="25" t="n"/>
+      <c r="J55" s="25" t="n"/>
+      <c r="K55" s="25" t="n"/>
+      <c r="L55" s="25" t="n"/>
+      <c r="M55" s="25" t="n"/>
+      <c r="N55" s="25" t="n"/>
+      <c r="O55" s="25" t="n"/>
+      <c r="P55" s="25" t="n"/>
+      <c r="Q55" s="25" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="n"/>
+      <c r="B56" s="25" t="n"/>
+      <c r="C56" s="25" t="n"/>
+      <c r="D56" s="25" t="n"/>
+      <c r="E56" s="25" t="n"/>
+      <c r="F56" s="25" t="n"/>
+      <c r="G56" s="25" t="n"/>
+      <c r="H56" s="25" t="n"/>
+      <c r="I56" s="25" t="n"/>
+      <c r="J56" s="25" t="n"/>
+      <c r="K56" s="25" t="n"/>
+      <c r="L56" s="25" t="n"/>
+      <c r="M56" s="25" t="n"/>
+      <c r="N56" s="25" t="n"/>
+      <c r="O56" s="25" t="n"/>
+      <c r="P56" s="25" t="n"/>
+      <c r="Q56" s="25" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="25" t="n"/>
+      <c r="B57" s="25" t="n"/>
+      <c r="C57" s="25" t="n"/>
+      <c r="D57" s="25" t="n"/>
+      <c r="E57" s="25" t="n"/>
+      <c r="F57" s="25" t="n"/>
+      <c r="G57" s="25" t="n"/>
+      <c r="H57" s="25" t="n"/>
+      <c r="I57" s="25" t="n"/>
+      <c r="J57" s="25" t="n"/>
+      <c r="K57" s="25" t="n"/>
+      <c r="L57" s="25" t="n"/>
+      <c r="M57" s="25" t="n"/>
+      <c r="N57" s="25" t="n"/>
+      <c r="O57" s="25" t="n"/>
+      <c r="P57" s="25" t="n"/>
+      <c r="Q57" s="25" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="25" t="n"/>
+      <c r="B58" s="25" t="n"/>
+      <c r="C58" s="25" t="n"/>
+      <c r="D58" s="25" t="n"/>
+      <c r="E58" s="25" t="n"/>
+      <c r="F58" s="25" t="n"/>
+      <c r="G58" s="25" t="n"/>
+      <c r="H58" s="25" t="n"/>
+      <c r="I58" s="25" t="n"/>
+      <c r="J58" s="25" t="n"/>
+      <c r="K58" s="25" t="n"/>
+      <c r="L58" s="25" t="n"/>
+      <c r="M58" s="25" t="n"/>
+      <c r="N58" s="25" t="n"/>
+      <c r="O58" s="25" t="n"/>
+      <c r="P58" s="25" t="n"/>
+      <c r="Q58" s="25" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="25" t="n"/>
+      <c r="B59" s="25" t="n"/>
+      <c r="C59" s="25" t="n"/>
+      <c r="D59" s="25" t="n"/>
+      <c r="E59" s="25" t="n"/>
+      <c r="F59" s="25" t="n"/>
+      <c r="G59" s="25" t="n"/>
+      <c r="H59" s="25" t="n"/>
+      <c r="I59" s="25" t="n"/>
+      <c r="J59" s="25" t="n"/>
+      <c r="K59" s="25" t="n"/>
+      <c r="L59" s="25" t="n"/>
+      <c r="M59" s="25" t="n"/>
+      <c r="N59" s="25" t="n"/>
+      <c r="O59" s="25" t="n"/>
+      <c r="P59" s="25" t="n"/>
+      <c r="Q59" s="25" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="25" t="n"/>
+      <c r="B60" s="25" t="n"/>
+      <c r="C60" s="25" t="n"/>
+      <c r="D60" s="25" t="n"/>
+      <c r="E60" s="25" t="n"/>
+      <c r="F60" s="25" t="n"/>
+      <c r="G60" s="25" t="n"/>
+      <c r="H60" s="25" t="n"/>
+      <c r="I60" s="25" t="n"/>
+      <c r="J60" s="25" t="n"/>
+      <c r="K60" s="25" t="n"/>
+      <c r="L60" s="25" t="n"/>
+      <c r="M60" s="25" t="n"/>
+      <c r="N60" s="25" t="n"/>
+      <c r="O60" s="25" t="n"/>
+      <c r="P60" s="25" t="n"/>
+      <c r="Q60" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
